--- a/erp-server/erp-server-file/src/main/resources/excel/plm/skuStdCostDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/skuStdCostDetail.xlsx
@@ -41,12 +41,12 @@
     <t>销售状态</t>
   </si>
   <si>
+    <t>标准成本[不含税]</t>
+  </si>
+  <si>
     <t>币别</t>
   </si>
   <si>
-    <t>标准成本[不含税]</t>
-  </si>
-  <si>
     <t>生效日期[包含]</t>
   </si>
   <si>
@@ -71,10 +71,10 @@
     <t>{.saleStateName}</t>
   </si>
   <si>
-    <t>{.currencySymbol}</t>
-  </si>
-  <si>
     <t>{.stdCostPrice}</t>
+  </si>
+  <si>
+    <t>{.currency}</t>
   </si>
   <si>
     <t>{.effectiveDate}</t>
@@ -708,7 +708,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -716,6 +716,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1036,9 +1039,8 @@
     <col min="2" max="2" width="28.125" customWidth="1"/>
     <col min="3" max="3" width="25.5" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
-    <col min="5" max="5" width="16.25" customWidth="1"/>
-    <col min="6" max="6" width="18.625" customWidth="1"/>
-    <col min="7" max="8" width="17.875" customWidth="1"/>
+    <col min="5" max="5" width="18.625" customWidth="1"/>
+    <col min="6" max="8" width="17.875" customWidth="1"/>
     <col min="9" max="9" width="20.125" customWidth="1"/>
     <col min="10" max="10" width="18.375" customWidth="1"/>
   </cols>
@@ -1088,7 +1090,7 @@
       <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">

--- a/erp-server/erp-server-file/src/main/resources/excel/plm/skuStdCostDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/skuStdCostDetail.xlsx
@@ -83,7 +83,7 @@
     <t>{.lastOutstockDate}</t>
   </si>
   <si>
-    <t>{.approveUserName}</t>
+    <t>{.updateUserName}</t>
   </si>
   <si>
     <t>{.updateTime}</t>
